--- a/input/geo_list_of_nodes - Excel.xlsx
+++ b/input/geo_list_of_nodes - Excel.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boissieremat\Documents\GitHub\antares-brinkerink-2015\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{56A303A1-EC40-4F72-91BC-A8706C46E9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6994059F-C135-4410-B05F-C7282D6BFE7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15390"/>
+    <workbookView xWindow="-25320" yWindow="-60" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geo_list_of_nodes" sheetId="2" r:id="rId1"/>
@@ -23,15 +23,15 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" keepAlive="1" name="Requête - geo_list_of_nodes - Excel" description="Connexion à la requête « geo_list_of_nodes - Excel » dans le classeur." type="5" refreshedVersion="8" background="1" saveData="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" keepAlive="1" name="Requête - geo_list_of_nodes - Excel" description="Connexion à la requête « geo_list_of_nodes - Excel » dans le classeur." type="5" refreshedVersion="8" background="1" saveData="1">
     <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=&quot;geo_list_of_nodes - Excel&quot;;Extended Properties=&quot;&quot;" command="SELECT * FROM [geo_list_of_nodes - Excel]"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="941">
   <si>
     <t>Node</t>
   </si>
@@ -2052,12 +2052,6 @@
     <t>Alaska</t>
   </si>
   <si>
-    <t>45.6875333395</t>
-  </si>
-  <si>
-    <t>-112.494333916</t>
-  </si>
-  <si>
     <t>NA-USA-AZ</t>
   </si>
   <si>
@@ -2656,12 +2650,216 @@
   </si>
   <si>
     <t>-106.141224</t>
+  </si>
+  <si>
+    <t>64.4459613</t>
+  </si>
+  <si>
+    <t>-149.680909</t>
+  </si>
+  <si>
+    <t>34.395342</t>
+  </si>
+  <si>
+    <t>-111.763275</t>
+  </si>
+  <si>
+    <t>OSM "Arizona"</t>
+  </si>
+  <si>
+    <t>36.7014631</t>
+  </si>
+  <si>
+    <t>-118.755997</t>
+  </si>
+  <si>
+    <t>OSM "California"</t>
+  </si>
+  <si>
+    <t>31.2638905</t>
+  </si>
+  <si>
+    <t>-98.5456116</t>
+  </si>
+  <si>
+    <t>OSM "Texas"</t>
+  </si>
+  <si>
+    <t>27.7567667</t>
+  </si>
+  <si>
+    <t>-81.4639835</t>
+  </si>
+  <si>
+    <t>OSM "Florida"</t>
+  </si>
+  <si>
+    <t>13.45011745</t>
+  </si>
+  <si>
+    <t>144.7577087765826</t>
+  </si>
+  <si>
+    <t>19.593801499999998</t>
+  </si>
+  <si>
+    <t>-155.42837009716908</t>
+  </si>
+  <si>
+    <t>44.4308975</t>
+  </si>
+  <si>
+    <t>-89.6884637</t>
+  </si>
+  <si>
+    <t>OSM "Wisconsin"</t>
+  </si>
+  <si>
+    <t>47.6201461</t>
+  </si>
+  <si>
+    <t>-100.540737</t>
+  </si>
+  <si>
+    <t>OSM "North Dakota"</t>
+  </si>
+  <si>
+    <t>43.4849133</t>
+  </si>
+  <si>
+    <t>-71.6553992</t>
+  </si>
+  <si>
+    <t>OSM "New Hampshire"</t>
+  </si>
+  <si>
+    <t>43.6447642</t>
+  </si>
+  <si>
+    <t>-114.015407</t>
+  </si>
+  <si>
+    <t>OSM "Idaho"</t>
+  </si>
+  <si>
+    <t>43.1561681</t>
+  </si>
+  <si>
+    <t>-75.8449946</t>
+  </si>
+  <si>
+    <t>OSM "New York State"</t>
+  </si>
+  <si>
+    <t>18.2247706</t>
+  </si>
+  <si>
+    <t>-66.4858295</t>
+  </si>
+  <si>
+    <t>38.7251776</t>
+  </si>
+  <si>
+    <t>-105.607716</t>
+  </si>
+  <si>
+    <t>OSM "Colorado"</t>
+  </si>
+  <si>
+    <t>40.9699889</t>
+  </si>
+  <si>
+    <t>-77.7278831</t>
+  </si>
+  <si>
+    <t>OSM "Pennsylvania"</t>
+  </si>
+  <si>
+    <t>43.6211955</t>
+  </si>
+  <si>
+    <t>-84.6824346</t>
+  </si>
+  <si>
+    <t>OSM "Michigan"</t>
+  </si>
+  <si>
+    <t>40.2253569</t>
+  </si>
+  <si>
+    <t>-82.6881395</t>
+  </si>
+  <si>
+    <t>OSM "Ohio"</t>
+  </si>
+  <si>
+    <t>35.2048883</t>
+  </si>
+  <si>
+    <t>-92.4479108</t>
+  </si>
+  <si>
+    <t>OSM "Arkansas"</t>
+  </si>
+  <si>
+    <t>35.7730076</t>
+  </si>
+  <si>
+    <t>-86.2820081</t>
+  </si>
+  <si>
+    <t>OSM "Tennessee"</t>
+  </si>
+  <si>
+    <t>33.2588817</t>
+  </si>
+  <si>
+    <t>-86.8295337</t>
+  </si>
+  <si>
+    <t>OSM "Alabama"</t>
+  </si>
+  <si>
+    <t>38.27312</t>
+  </si>
+  <si>
+    <t>-98.5821872</t>
+  </si>
+  <si>
+    <t>OSM "Kansas"</t>
+  </si>
+  <si>
+    <t>34.9550817</t>
+  </si>
+  <si>
+    <t>-97.2684063</t>
+  </si>
+  <si>
+    <t>OSM "Oklahoma"</t>
+  </si>
+  <si>
+    <t>35.6729639</t>
+  </si>
+  <si>
+    <t>-79.0392919</t>
+  </si>
+  <si>
+    <t>OSM "North Carolina"</t>
+  </si>
+  <si>
+    <t>38.7604815</t>
+  </si>
+  <si>
+    <t>-92.5617875</t>
+  </si>
+  <si>
+    <t>OSM "Missouri"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3190,10 +3388,10 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -3226,12 +3424,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="DonnéesExternes_1" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DonnéesExternes_1" connectionId="1" xr16:uid="{00000000-0016-0000-0000-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="8">
     <queryTableFields count="7">
       <queryTableField id="1" name="Column1" tableColumnId="1"/>
@@ -3247,16 +3441,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="geo_list_of_nodes___Excel" displayName="geo_list_of_nodes___Excel" ref="A1:G259" tableType="queryTable" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:G259"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="geo_list_of_nodes___Excel" displayName="geo_list_of_nodes___Excel" ref="A1:G259" tableType="queryTable" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="A1:G259" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" uniqueName="1" name="Node" queryTableFieldId="1" dataDxfId="7"/>
-    <tableColumn id="2" uniqueName="2" name="Continent" queryTableFieldId="2" dataDxfId="6"/>
-    <tableColumn id="3" uniqueName="3" name="Country" queryTableFieldId="3" dataDxfId="5"/>
-    <tableColumn id="4" uniqueName="4" name="Geographical region" queryTableFieldId="4" dataDxfId="3"/>
-    <tableColumn id="5" uniqueName="5" name="lat" queryTableFieldId="5" dataDxfId="2"/>
-    <tableColumn id="6" uniqueName="6" name="lon" queryTableFieldId="6" dataDxfId="0"/>
-    <tableColumn id="7" uniqueName="7" name="coordinates_source" queryTableFieldId="7" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" uniqueName="1" name="Node" queryTableFieldId="1" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" uniqueName="2" name="Continent" queryTableFieldId="2" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" uniqueName="3" name="Country" queryTableFieldId="3" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" uniqueName="4" name="Geographical region" queryTableFieldId="4" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" uniqueName="5" name="lat" queryTableFieldId="5" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" uniqueName="6" name="lon" queryTableFieldId="6" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" uniqueName="7" name="coordinates_source" queryTableFieldId="7" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3558,20 +3752,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G259"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3582,7 +3776,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -3594,7 +3788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3617,7 +3811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3640,7 +3834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -3663,7 +3857,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -3686,7 +3880,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -3709,7 +3903,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -3732,7 +3926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
@@ -3755,7 +3949,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
@@ -3778,7 +3972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
@@ -3801,7 +3995,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
@@ -3824,7 +4018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -3847,7 +4041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>44</v>
       </c>
@@ -3870,7 +4064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,7 +4087,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>52</v>
       </c>
@@ -3916,7 +4110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>56</v>
       </c>
@@ -3939,7 +4133,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>60</v>
       </c>
@@ -3959,10 +4153,10 @@
         <v>-13.892143024999999</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>62</v>
       </c>
@@ -3985,7 +4179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>66</v>
       </c>
@@ -4008,7 +4202,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>70</v>
       </c>
@@ -4031,7 +4225,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>74</v>
       </c>
@@ -4054,7 +4248,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>78</v>
       </c>
@@ -4077,7 +4271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>82</v>
       </c>
@@ -4100,7 +4294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>86</v>
       </c>
@@ -4123,7 +4317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>90</v>
       </c>
@@ -4146,7 +4340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>94</v>
       </c>
@@ -4169,7 +4363,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>98</v>
       </c>
@@ -4192,7 +4386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>100</v>
       </c>
@@ -4215,7 +4409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>104</v>
       </c>
@@ -4238,7 +4432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>108</v>
       </c>
@@ -4261,7 +4455,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>112</v>
       </c>
@@ -4284,7 +4478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>116</v>
       </c>
@@ -4307,7 +4501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>120</v>
       </c>
@@ -4330,7 +4524,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>124</v>
       </c>
@@ -4353,7 +4547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>128</v>
       </c>
@@ -4376,7 +4570,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>132</v>
       </c>
@@ -4399,7 +4593,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>136</v>
       </c>
@@ -4422,7 +4616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>140</v>
       </c>
@@ -4445,7 +4639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>144</v>
       </c>
@@ -4468,7 +4662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>148</v>
       </c>
@@ -4491,7 +4685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>150</v>
       </c>
@@ -4514,7 +4708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>154</v>
       </c>
@@ -4537,7 +4731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>158</v>
       </c>
@@ -4560,7 +4754,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>162</v>
       </c>
@@ -4583,7 +4777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>166</v>
       </c>
@@ -4606,7 +4800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>170</v>
       </c>
@@ -4629,7 +4823,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>172</v>
       </c>
@@ -4652,7 +4846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>176</v>
       </c>
@@ -4675,7 +4869,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>180</v>
       </c>
@@ -4698,7 +4892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>184</v>
       </c>
@@ -4721,7 +4915,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>188</v>
       </c>
@@ -4744,7 +4938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>193</v>
       </c>
@@ -4767,7 +4961,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>197</v>
       </c>
@@ -4790,7 +4984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>201</v>
       </c>
@@ -4813,7 +5007,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>205</v>
       </c>
@@ -4836,7 +5030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>207</v>
       </c>
@@ -4859,7 +5053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>211</v>
       </c>
@@ -4879,10 +5073,10 @@
         <v>215</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>216</v>
       </c>
@@ -4902,10 +5096,10 @@
         <v>215</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>218</v>
       </c>
@@ -4925,10 +5119,10 @@
         <v>215</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>220</v>
       </c>
@@ -4948,10 +5142,10 @@
         <v>215</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>222</v>
       </c>
@@ -4971,10 +5165,10 @@
         <v>215</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>224</v>
       </c>
@@ -4994,10 +5188,10 @@
         <v>215</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>226</v>
       </c>
@@ -5017,10 +5211,10 @@
         <v>215</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>228</v>
       </c>
@@ -5040,10 +5234,10 @@
         <v>215</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>230</v>
       </c>
@@ -5063,10 +5257,10 @@
         <v>215</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>232</v>
       </c>
@@ -5086,10 +5280,10 @@
         <v>215</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>234</v>
       </c>
@@ -5109,10 +5303,10 @@
         <v>215</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>236</v>
       </c>
@@ -5132,10 +5326,10 @@
         <v>215</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>238</v>
       </c>
@@ -5155,10 +5349,10 @@
         <v>215</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>240</v>
       </c>
@@ -5178,10 +5372,10 @@
         <v>215</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>242</v>
       </c>
@@ -5201,10 +5395,10 @@
         <v>215</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>244</v>
       </c>
@@ -5224,10 +5418,10 @@
         <v>215</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>246</v>
       </c>
@@ -5247,10 +5441,10 @@
         <v>215</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>248</v>
       </c>
@@ -5270,10 +5464,10 @@
         <v>215</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>250</v>
       </c>
@@ -5293,10 +5487,10 @@
         <v>215</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>252</v>
       </c>
@@ -5316,10 +5510,10 @@
         <v>215</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>254</v>
       </c>
@@ -5339,10 +5533,10 @@
         <v>215</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>256</v>
       </c>
@@ -5362,10 +5556,10 @@
         <v>215</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>258</v>
       </c>
@@ -5385,10 +5579,10 @@
         <v>215</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>260</v>
       </c>
@@ -5408,10 +5602,10 @@
         <v>215</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>262</v>
       </c>
@@ -5431,10 +5625,10 @@
         <v>215</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>264</v>
       </c>
@@ -5454,10 +5648,10 @@
         <v>215</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>266</v>
       </c>
@@ -5477,10 +5671,10 @@
         <v>215</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>268</v>
       </c>
@@ -5500,10 +5694,10 @@
         <v>215</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>270</v>
       </c>
@@ -5523,10 +5717,10 @@
         <v>215</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>272</v>
       </c>
@@ -5546,10 +5740,10 @@
         <v>215</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>274</v>
       </c>
@@ -5569,10 +5763,10 @@
         <v>215</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>276</v>
       </c>
@@ -5592,10 +5786,10 @@
         <v>215</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>278</v>
       </c>
@@ -5615,10 +5809,10 @@
         <v>215</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>280</v>
       </c>
@@ -5638,10 +5832,10 @@
         <v>215</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>282</v>
       </c>
@@ -5664,7 +5858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>286</v>
       </c>
@@ -5687,7 +5881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>291</v>
       </c>
@@ -5710,7 +5904,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>293</v>
       </c>
@@ -5733,7 +5927,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>295</v>
       </c>
@@ -5756,7 +5950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>297</v>
       </c>
@@ -5779,7 +5973,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>299</v>
       </c>
@@ -5802,7 +5996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>301</v>
       </c>
@@ -5825,7 +6019,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>305</v>
       </c>
@@ -5848,7 +6042,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>307</v>
       </c>
@@ -5871,7 +6065,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>311</v>
       </c>
@@ -5894,7 +6088,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>316</v>
       </c>
@@ -5917,7 +6111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>318</v>
       </c>
@@ -5940,7 +6134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>320</v>
       </c>
@@ -5963,7 +6157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>322</v>
       </c>
@@ -5986,7 +6180,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>324</v>
       </c>
@@ -6009,7 +6203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>326</v>
       </c>
@@ -6032,7 +6226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>330</v>
       </c>
@@ -6055,7 +6249,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>334</v>
       </c>
@@ -6078,7 +6272,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>338</v>
       </c>
@@ -6101,7 +6295,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>340</v>
       </c>
@@ -6124,7 +6318,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>344</v>
       </c>
@@ -6147,7 +6341,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>346</v>
       </c>
@@ -6170,7 +6364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>350</v>
       </c>
@@ -6193,7 +6387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>354</v>
       </c>
@@ -6216,7 +6410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>358</v>
       </c>
@@ -6239,7 +6433,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>362</v>
       </c>
@@ -6262,7 +6456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>366</v>
       </c>
@@ -6285,7 +6479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>370</v>
       </c>
@@ -6308,7 +6502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>374</v>
       </c>
@@ -6331,7 +6525,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>378</v>
       </c>
@@ -6354,7 +6548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>382</v>
       </c>
@@ -6377,7 +6571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>384</v>
       </c>
@@ -6400,7 +6594,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>388</v>
       </c>
@@ -6423,7 +6617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>391</v>
       </c>
@@ -6446,7 +6640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>393</v>
       </c>
@@ -6469,7 +6663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>395</v>
       </c>
@@ -6492,7 +6686,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>397</v>
       </c>
@@ -6515,7 +6709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>399</v>
       </c>
@@ -6538,7 +6732,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>401</v>
       </c>
@@ -6561,7 +6755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>403</v>
       </c>
@@ -6584,7 +6778,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>407</v>
       </c>
@@ -6607,7 +6801,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>411</v>
       </c>
@@ -6630,7 +6824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>413</v>
       </c>
@@ -6653,7 +6847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>417</v>
       </c>
@@ -6676,7 +6870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>421</v>
       </c>
@@ -6699,7 +6893,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>425</v>
       </c>
@@ -6722,7 +6916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>429</v>
       </c>
@@ -6745,7 +6939,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>431</v>
       </c>
@@ -6768,7 +6962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>435</v>
       </c>
@@ -6791,7 +6985,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>437</v>
       </c>
@@ -6814,7 +7008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>441</v>
       </c>
@@ -6837,7 +7031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>446</v>
       </c>
@@ -6860,7 +7054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>450</v>
       </c>
@@ -6883,7 +7077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>454</v>
       </c>
@@ -6906,7 +7100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>458</v>
       </c>
@@ -6929,7 +7123,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>462</v>
       </c>
@@ -6952,7 +7146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>466</v>
       </c>
@@ -6975,7 +7169,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>470</v>
       </c>
@@ -6998,7 +7192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>474</v>
       </c>
@@ -7021,7 +7215,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>478</v>
       </c>
@@ -7044,7 +7238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>482</v>
       </c>
@@ -7067,7 +7261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>486</v>
       </c>
@@ -7090,7 +7284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>490</v>
       </c>
@@ -7113,7 +7307,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>494</v>
       </c>
@@ -7136,7 +7330,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>498</v>
       </c>
@@ -7159,7 +7353,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>502</v>
       </c>
@@ -7182,7 +7376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>506</v>
       </c>
@@ -7205,7 +7399,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>510</v>
       </c>
@@ -7228,7 +7422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>514</v>
       </c>
@@ -7251,7 +7445,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>518</v>
       </c>
@@ -7274,7 +7468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>522</v>
       </c>
@@ -7297,7 +7491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>526</v>
       </c>
@@ -7320,7 +7514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>530</v>
       </c>
@@ -7343,7 +7537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>534</v>
       </c>
@@ -7366,7 +7560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>538</v>
       </c>
@@ -7389,7 +7583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>542</v>
       </c>
@@ -7412,7 +7606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>546</v>
       </c>
@@ -7435,7 +7629,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>550</v>
       </c>
@@ -7458,7 +7652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>554</v>
       </c>
@@ -7481,7 +7675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>558</v>
       </c>
@@ -7504,7 +7698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>560</v>
       </c>
@@ -7527,7 +7721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>562</v>
       </c>
@@ -7550,7 +7744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>566</v>
       </c>
@@ -7573,7 +7767,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>570</v>
       </c>
@@ -7596,7 +7790,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>574</v>
       </c>
@@ -7619,7 +7813,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>578</v>
       </c>
@@ -7642,7 +7836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>582</v>
       </c>
@@ -7665,7 +7859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>586</v>
       </c>
@@ -7688,7 +7882,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>590</v>
       </c>
@@ -7711,7 +7905,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>594</v>
       </c>
@@ -7734,7 +7928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>598</v>
       </c>
@@ -7757,7 +7951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>602</v>
       </c>
@@ -7780,7 +7974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>606</v>
       </c>
@@ -7794,16 +7988,16 @@
         <v>609</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>610</v>
       </c>
@@ -7817,16 +8011,16 @@
         <v>611</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>612</v>
       </c>
@@ -7840,16 +8034,16 @@
         <v>613</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>614</v>
       </c>
@@ -7863,16 +8057,16 @@
         <v>615</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>616</v>
       </c>
@@ -7886,16 +8080,16 @@
         <v>617</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>618</v>
       </c>
@@ -7909,16 +8103,16 @@
         <v>619</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>620</v>
       </c>
@@ -7932,16 +8126,16 @@
         <v>621</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>622</v>
       </c>
@@ -7955,16 +8149,16 @@
         <v>623</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>624</v>
       </c>
@@ -7978,16 +8172,16 @@
         <v>625</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>626</v>
       </c>
@@ -8010,7 +8204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>630</v>
       </c>
@@ -8033,7 +8227,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>634</v>
       </c>
@@ -8056,7 +8250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>638</v>
       </c>
@@ -8079,7 +8273,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>642</v>
       </c>
@@ -8102,7 +8296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>646</v>
       </c>
@@ -8125,7 +8319,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>650</v>
       </c>
@@ -8148,7 +8342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>654</v>
       </c>
@@ -8171,7 +8365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>658</v>
       </c>
@@ -8194,7 +8388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>662</v>
       </c>
@@ -8217,7 +8411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>666</v>
       </c>
@@ -8240,7 +8434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>670</v>
       </c>
@@ -8254,18 +8448,18 @@
         <v>672</v>
       </c>
       <c r="E204" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="F204" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="G204" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A205" s="1" t="s">
-        <v>675</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>607</v>
@@ -8274,21 +8468,21 @@
         <v>671</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>673</v>
+        <v>875</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>674</v>
+        <v>876</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>607</v>
@@ -8297,21 +8491,21 @@
         <v>671</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>673</v>
+        <v>878</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>674</v>
+        <v>879</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>607</v>
@@ -8320,21 +8514,21 @@
         <v>671</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>673</v>
+        <v>881</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>674</v>
+        <v>882</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>607</v>
@@ -8343,21 +8537,21 @@
         <v>671</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>673</v>
+        <v>884</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>674</v>
+        <v>885</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>607</v>
@@ -8366,21 +8560,21 @@
         <v>671</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>673</v>
+        <v>887</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>674</v>
+        <v>888</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>607</v>
@@ -8389,21 +8583,21 @@
         <v>671</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>673</v>
+        <v>889</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>674</v>
+        <v>890</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>607</v>
@@ -8412,21 +8606,21 @@
         <v>671</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>673</v>
+        <v>891</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>674</v>
+        <v>892</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>607</v>
@@ -8435,21 +8629,21 @@
         <v>671</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>673</v>
+        <v>894</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>674</v>
+        <v>895</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>607</v>
@@ -8458,21 +8652,21 @@
         <v>671</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>673</v>
+        <v>897</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>674</v>
+        <v>898</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>607</v>
@@ -8481,21 +8675,21 @@
         <v>671</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>673</v>
+        <v>900</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>674</v>
+        <v>901</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>607</v>
@@ -8504,21 +8698,21 @@
         <v>671</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>673</v>
+        <v>903</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>674</v>
+        <v>904</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>607</v>
@@ -8527,21 +8721,21 @@
         <v>671</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>673</v>
+        <v>906</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>674</v>
+        <v>907</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>607</v>
@@ -8550,21 +8744,21 @@
         <v>671</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>673</v>
+        <v>908</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>674</v>
+        <v>909</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>607</v>
@@ -8573,21 +8767,21 @@
         <v>671</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>673</v>
+        <v>911</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>674</v>
+        <v>912</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>607</v>
@@ -8596,21 +8790,21 @@
         <v>671</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>673</v>
+        <v>914</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>674</v>
+        <v>915</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>607</v>
@@ -8619,21 +8813,21 @@
         <v>671</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>673</v>
+        <v>917</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>674</v>
+        <v>918</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>607</v>
@@ -8642,21 +8836,21 @@
         <v>671</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>673</v>
+        <v>920</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>674</v>
+        <v>921</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>607</v>
@@ -8665,21 +8859,21 @@
         <v>671</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>673</v>
+        <v>923</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>674</v>
+        <v>924</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>607</v>
@@ -8688,21 +8882,21 @@
         <v>671</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>673</v>
+        <v>926</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>674</v>
+        <v>927</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>607</v>
@@ -8711,21 +8905,21 @@
         <v>671</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>673</v>
+        <v>929</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>674</v>
+        <v>930</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>607</v>
@@ -8734,21 +8928,21 @@
         <v>671</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>673</v>
+        <v>932</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>674</v>
+        <v>933</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>607</v>
@@ -8757,21 +8951,21 @@
         <v>671</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>673</v>
+        <v>935</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>674</v>
+        <v>936</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>607</v>
@@ -8780,30 +8974,30 @@
         <v>671</v>
       </c>
       <c r="D227" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="E227" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="G227" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A228" s="1" t="s">
+      <c r="C228" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>723</v>
-      </c>
       <c r="D228" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E228" s="2">
         <v>-79.406307499999997</v>
@@ -8812,596 +9006,596 @@
         <v>0.31493120000000002</v>
       </c>
       <c r="G228" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E229" s="2" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A229" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C229" s="1" t="s">
+      <c r="F229" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="D229" s="1" t="s">
+      <c r="B230" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="E229" s="2" t="s">
+      <c r="E230" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="F229" s="2" t="s">
+      <c r="F230" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="G229" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A230" s="1" t="s">
+      <c r="G230" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="D230" s="1" t="s">
+      <c r="B231" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D231" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="E230" s="2" t="s">
+      <c r="E231" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="F230" s="2" t="s">
+      <c r="F231" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="G230" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A231" s="1" t="s">
+      <c r="G231" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="D231" s="1" t="s">
+      <c r="B232" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D232" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="E231" s="2" t="s">
+      <c r="E232" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="F231" s="2" t="s">
+      <c r="F232" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="G231" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A232" s="1" t="s">
+      <c r="G232" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="D232" s="1" t="s">
+      <c r="B233" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D233" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="E232" s="2" t="s">
+      <c r="E233" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="F232" s="2" t="s">
+      <c r="F233" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="G232" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A233" s="1" t="s">
+      <c r="G233" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="D233" s="1" t="s">
+      <c r="B234" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="E233" s="2" t="s">
+      <c r="E234" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="F233" s="2" t="s">
+      <c r="F234" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="G233" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A234" s="1" t="s">
+      <c r="G234" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="D234" s="1" t="s">
+      <c r="B235" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="E234" s="2" t="s">
+      <c r="E235" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="F234" s="2" t="s">
+      <c r="F235" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="G234" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A235" s="1" t="s">
+      <c r="G235" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="D235" s="1" t="s">
+      <c r="B236" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C236" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="E235" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="G235" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A236" s="1" t="s">
+      <c r="D236" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="E236" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C236" s="1" t="s">
+      <c r="F236" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="D236" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="E236" s="2" t="s">
+      <c r="G236" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="F236" s="2" t="s">
+      <c r="B237" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C237" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="G236" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A237" s="1" t="s">
+      <c r="D237" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="E237" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C237" s="1" t="s">
+      <c r="F237" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="D237" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="E237" s="2" t="s">
+      <c r="G237" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="F237" s="2" t="s">
+      <c r="B238" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C238" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="G237" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A238" s="1" t="s">
+      <c r="D238" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="E238" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C238" s="1" t="s">
+      <c r="F238" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="D238" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="E238" s="2" t="s">
+      <c r="G238" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="F238" s="2" t="s">
+      <c r="B239" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="G238" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A239" s="1" t="s">
+      <c r="C239" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="D239" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="E239" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="C239" s="1" t="s">
+      <c r="F239" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="D239" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="E239" s="2" t="s">
+      <c r="G239" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="F239" s="2" t="s">
+      <c r="B240" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C240" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="G239" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A240" s="1" t="s">
+      <c r="D240" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="E240" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C240" s="1" t="s">
+      <c r="F240" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="D240" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E240" s="2" t="s">
+      <c r="G240" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="F240" s="2" t="s">
+      <c r="B241" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C241" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="G240" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A241" s="1" t="s">
+      <c r="D241" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C241" s="1" t="s">
+      <c r="E241" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="G241" s="1" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="D241" s="1" t="s">
+      <c r="B242" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="E241" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="F241" s="2" t="s">
+      <c r="E242" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="G241" s="1" t="s">
+      <c r="F242" s="2" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A242" s="1" t="s">
+      <c r="G242" s="1" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="D242" s="1" t="s">
+      <c r="B243" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D243" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="E242" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="F242" s="2" t="s">
+      <c r="E243" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="G243" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="G242" s="1" t="s">
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="G244" s="1" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A243" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>840</v>
-      </c>
-      <c r="G243" s="1" t="s">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="G245" s="1" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A244" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="G244" s="1" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A245" s="1" t="s">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="G245" s="1" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A246" s="1" t="s">
-        <v>771</v>
-      </c>
       <c r="B246" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>292</v>
       </c>
       <c r="E246" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="G246" s="1" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="G247" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="E248" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="F246" s="2" t="s">
+      <c r="F248" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="G246" s="1" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A247" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="D247" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="G247" s="1" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A248" s="1" t="s">
+      <c r="G248" s="1" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="B248" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="F248" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="G248" s="1" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A249" s="1" t="s">
-        <v>776</v>
-      </c>
       <c r="B249" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>296</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>298</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="E251" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C251" s="1" t="s">
+      <c r="F251" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="D251" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="E251" s="2" t="s">
+      <c r="G251" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="F251" s="2" t="s">
+      <c r="B252" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C252" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="G251" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A252" s="1" t="s">
+      <c r="D252" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="E252" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C252" s="1" t="s">
+      <c r="F252" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="D252" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="E252" s="2" t="s">
+      <c r="G252" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="F252" s="2" t="s">
+      <c r="B253" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C253" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="G252" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A253" s="1" t="s">
+      <c r="D253" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C253" s="1" t="s">
+      <c r="F253" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="D253" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="E253" s="2" t="s">
+      <c r="G253" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="F253" s="2" t="s">
+      <c r="B254" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C254" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="G253" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A254" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>791</v>
-      </c>
       <c r="D254" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="E254" s="2">
         <v>4.0039882000000002</v>
@@ -9413,113 +9607,113 @@
         <v>10</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="E255" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C255" s="1" t="s">
+      <c r="F255" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="D255" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="E255" s="2" t="s">
+      <c r="G255" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="F255" s="2" t="s">
+      <c r="B256" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C256" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="G255" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A256" s="1" t="s">
+      <c r="D256" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="E256" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C256" s="1" t="s">
+      <c r="F256" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="D256" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="E256" s="2" t="s">
+      <c r="G256" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="F256" s="2" t="s">
+      <c r="B257" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C257" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="G256" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A257" s="1" t="s">
+      <c r="D257" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="E257" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C257" s="1" t="s">
+      <c r="F257" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="D257" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="E257" s="2" t="s">
+      <c r="G257" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="F257" s="2" t="s">
+      <c r="B258" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C258" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="G257" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A258" s="1" t="s">
+      <c r="D258" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C258" s="1" t="s">
+      <c r="F258" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="D258" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="E258" s="2" t="s">
+      <c r="G258" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="F258" s="2" t="s">
+      <c r="B259" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C259" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="G258" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A259" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="C259" s="1" t="s">
-        <v>809</v>
-      </c>
       <c r="D259" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F259" s="2">
         <v>-66.169397250800003</v>

--- a/input/geo_list_of_nodes - Excel.xlsx
+++ b/input/geo_list_of_nodes - Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boissieremat\Documents\GitHub\antares-brinkerink-2015\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6994059F-C135-4410-B05F-C7282D6BFE7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDE4466-AD8C-493F-AE3D-11AAE7A7EC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="-60" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="geo_list_of_nodes" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="DonnéesExternes_1" localSheetId="0" hidden="1">geo_list_of_nodes!$A$1:$G$259</definedName>
+    <definedName name="DonnéesExternes_1" localSheetId="0" hidden="1">geo_list_of_nodes!$A$1:$G$262</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="953">
   <si>
     <t>Node</t>
   </si>
@@ -2854,6 +2854,42 @@
   </si>
   <si>
     <t>OSM "Missouri"</t>
+  </si>
+  <si>
+    <t>AF-SOM</t>
+  </si>
+  <si>
+    <t>Somalia</t>
+  </si>
+  <si>
+    <t>4.74860896352</t>
+  </si>
+  <si>
+    <t>45.7059511133</t>
+  </si>
+  <si>
+    <t>AF-TCD</t>
+  </si>
+  <si>
+    <t>Chad</t>
+  </si>
+  <si>
+    <t>15.332983539</t>
+  </si>
+  <si>
+    <t>18.6461890475</t>
+  </si>
+  <si>
+    <t>AS-TLS</t>
+  </si>
+  <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
+    <t>-8.8233219641</t>
+  </si>
+  <si>
+    <t>125.85227581</t>
   </si>
 </sst>
 </file>
@@ -3441,8 +3477,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="geo_list_of_nodes___Excel" displayName="geo_list_of_nodes___Excel" ref="A1:G259" tableType="queryTable" totalsRowShown="0" headerRowDxfId="7">
-  <autoFilter ref="A1:G259" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="geo_list_of_nodes___Excel" displayName="geo_list_of_nodes___Excel" ref="A1:G262" tableType="queryTable" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="A1:G262" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" uniqueName="1" name="Node" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" uniqueName="2" name="Continent" queryTableFieldId="2" dataDxfId="5"/>
@@ -3753,7 +3789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G259"/>
+  <dimension ref="A1:G262"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -4664,22 +4700,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>148</v>
+        <v>941</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>149</v>
+        <v>942</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" s="2">
-        <v>15.9868153397</v>
-      </c>
-      <c r="F40" s="2">
-        <v>29.9397656232</v>
+        <v>942</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>944</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>10</v>
@@ -4687,22 +4723,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
+      </c>
+      <c r="E41" s="2">
+        <v>15.9868153397</v>
+      </c>
+      <c r="F41" s="2">
+        <v>29.9397656232</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>10</v>
@@ -4710,22 +4746,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>10</v>
@@ -4733,22 +4769,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>10</v>
@@ -4756,22 +4792,22 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>10</v>
@@ -4779,22 +4815,22 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>166</v>
+        <v>945</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>167</v>
+        <v>946</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>167</v>
+        <v>946</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>168</v>
+        <v>947</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>169</v>
+        <v>948</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>10</v>
@@ -4802,22 +4838,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E46" s="2">
-        <v>-6.2750448303899997</v>
-      </c>
-      <c r="F46" s="2">
-        <v>34.813467624300003</v>
+        <v>163</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>10</v>
@@ -4825,22 +4861,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>10</v>
@@ -4848,22 +4884,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
+      </c>
+      <c r="E48" s="2">
+        <v>-6.2750448303899997</v>
+      </c>
+      <c r="F48" s="2">
+        <v>34.813467624300003</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>10</v>
@@ -4871,22 +4907,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>10</v>
@@ -4894,22 +4930,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>10</v>
@@ -4917,22 +4953,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>189</v>
+        <v>7</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>10</v>
@@ -4940,22 +4976,22 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>189</v>
+        <v>7</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>10</v>
@@ -4963,22 +4999,22 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>10</v>
@@ -4986,22 +5022,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>10</v>
@@ -5009,22 +5045,22 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E55" s="2">
-        <v>4.5167995377099999</v>
-      </c>
-      <c r="F55" s="2">
-        <v>114.727238056</v>
+        <v>198</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>10</v>
@@ -5032,22 +5068,22 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>10</v>
@@ -5055,53 +5091,53 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>215</v>
+        <v>206</v>
+      </c>
+      <c r="E57" s="2">
+        <v>4.5167995377099999</v>
+      </c>
+      <c r="F57" s="2">
+        <v>114.727238056</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>809</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>809</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>189</v>
@@ -5110,7 +5146,7 @@
         <v>212</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>214</v>
@@ -5124,7 +5160,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>189</v>
@@ -5133,7 +5169,7 @@
         <v>212</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>214</v>
@@ -5147,7 +5183,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>189</v>
@@ -5156,7 +5192,7 @@
         <v>212</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>214</v>
@@ -5170,7 +5206,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>189</v>
@@ -5179,7 +5215,7 @@
         <v>212</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>214</v>
@@ -5193,7 +5229,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>189</v>
@@ -5202,7 +5238,7 @@
         <v>212</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>214</v>
@@ -5216,7 +5252,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>189</v>
@@ -5225,7 +5261,7 @@
         <v>212</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>214</v>
@@ -5239,7 +5275,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>189</v>
@@ -5248,7 +5284,7 @@
         <v>212</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>214</v>
@@ -5262,7 +5298,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>189</v>
@@ -5271,7 +5307,7 @@
         <v>212</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>214</v>
@@ -5285,7 +5321,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>189</v>
@@ -5294,7 +5330,7 @@
         <v>212</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>214</v>
@@ -5308,7 +5344,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>189</v>
@@ -5317,7 +5353,7 @@
         <v>212</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>214</v>
@@ -5331,7 +5367,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>189</v>
@@ -5340,7 +5376,7 @@
         <v>212</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>214</v>
@@ -5354,7 +5390,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>189</v>
@@ -5363,7 +5399,7 @@
         <v>212</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>214</v>
@@ -5377,7 +5413,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>189</v>
@@ -5386,7 +5422,7 @@
         <v>212</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>214</v>
@@ -5400,7 +5436,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>189</v>
@@ -5409,7 +5445,7 @@
         <v>212</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>214</v>
@@ -5423,7 +5459,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>189</v>
@@ -5432,7 +5468,7 @@
         <v>212</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>214</v>
@@ -5446,7 +5482,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>189</v>
@@ -5455,7 +5491,7 @@
         <v>212</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>214</v>
@@ -5469,7 +5505,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>189</v>
@@ -5478,7 +5514,7 @@
         <v>212</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>214</v>
@@ -5492,7 +5528,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>189</v>
@@ -5501,7 +5537,7 @@
         <v>212</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>214</v>
@@ -5515,7 +5551,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>189</v>
@@ -5524,7 +5560,7 @@
         <v>212</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>214</v>
@@ -5538,7 +5574,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>189</v>
@@ -5547,7 +5583,7 @@
         <v>212</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>214</v>
@@ -5561,7 +5597,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>189</v>
@@ -5570,7 +5606,7 @@
         <v>212</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>214</v>
@@ -5584,7 +5620,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>189</v>
@@ -5593,7 +5629,7 @@
         <v>212</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>214</v>
@@ -5607,7 +5643,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>189</v>
@@ -5616,7 +5652,7 @@
         <v>212</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>214</v>
@@ -5630,7 +5666,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>189</v>
@@ -5639,7 +5675,7 @@
         <v>212</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>214</v>
@@ -5653,7 +5689,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>189</v>
@@ -5662,7 +5698,7 @@
         <v>212</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>214</v>
@@ -5676,7 +5712,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>189</v>
@@ -5685,7 +5721,7 @@
         <v>212</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>214</v>
@@ -5699,7 +5735,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>189</v>
@@ -5708,7 +5744,7 @@
         <v>212</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>214</v>
@@ -5722,7 +5758,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>189</v>
@@ -5731,7 +5767,7 @@
         <v>212</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>214</v>
@@ -5745,7 +5781,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>189</v>
@@ -5754,7 +5790,7 @@
         <v>212</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>214</v>
@@ -5768,7 +5804,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>189</v>
@@ -5777,7 +5813,7 @@
         <v>212</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>214</v>
@@ -5791,7 +5827,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>189</v>
@@ -5800,7 +5836,7 @@
         <v>212</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>214</v>
@@ -5814,7 +5850,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>189</v>
@@ -5823,7 +5859,7 @@
         <v>212</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>214</v>
@@ -5837,68 +5873,68 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>283</v>
+        <v>212</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>284</v>
+        <v>214</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>285</v>
+        <v>215</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>10</v>
+        <v>809</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>287</v>
+        <v>212</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>289</v>
+        <v>214</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>290</v>
+        <v>215</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>10</v>
+        <v>809</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>10</v>
@@ -5906,7 +5942,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>189</v>
@@ -5915,7 +5951,7 @@
         <v>287</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>289</v>
@@ -5929,7 +5965,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>189</v>
@@ -5938,7 +5974,7 @@
         <v>287</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>289</v>
@@ -5952,7 +5988,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>189</v>
@@ -5961,7 +5997,7 @@
         <v>287</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>289</v>
@@ -5975,22 +6011,22 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E97" s="2">
-        <v>32.570532586399999</v>
-      </c>
-      <c r="F97" s="2">
-        <v>54.277110854699998</v>
+        <v>296</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>290</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>10</v>
@@ -5998,22 +6034,22 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>10</v>
@@ -6021,22 +6057,22 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E99" s="2">
-        <v>31.4448606644</v>
+        <v>32.570532586399999</v>
       </c>
       <c r="F99" s="2">
-        <v>34.996423450499996</v>
+        <v>54.277110854699998</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>10</v>
@@ -6044,22 +6080,22 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>10</v>
@@ -6067,22 +6103,22 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>315</v>
+        <v>306</v>
+      </c>
+      <c r="E101" s="2">
+        <v>31.4448606644</v>
+      </c>
+      <c r="F101" s="2">
+        <v>34.996423450499996</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>10</v>
@@ -6090,22 +6126,22 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>10</v>
@@ -6113,7 +6149,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>189</v>
@@ -6122,7 +6158,7 @@
         <v>312</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>314</v>
@@ -6136,7 +6172,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>189</v>
@@ -6145,7 +6181,7 @@
         <v>312</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>314</v>
@@ -6159,7 +6195,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>189</v>
@@ -6168,7 +6204,7 @@
         <v>312</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>314</v>
@@ -6182,7 +6218,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>189</v>
@@ -6191,7 +6227,7 @@
         <v>312</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>314</v>
@@ -6205,22 +6241,22 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>10</v>
@@ -6228,22 +6264,22 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>10</v>
@@ -6251,22 +6287,22 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>10</v>
@@ -6274,22 +6310,22 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E110" s="2">
-        <v>36.3740505763</v>
-      </c>
-      <c r="F110" s="2">
-        <v>127.819686447</v>
+        <v>331</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>10</v>
@@ -6297,22 +6333,22 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>10</v>
@@ -6320,22 +6356,22 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="E112" s="2">
-        <v>18.502725460899999</v>
+        <v>36.3740505763</v>
       </c>
       <c r="F112" s="2">
-        <v>103.73756404</v>
+        <v>127.819686447</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>10</v>
@@ -6343,22 +6379,22 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>10</v>
@@ -6366,22 +6402,22 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>353</v>
+        <v>345</v>
+      </c>
+      <c r="E114" s="2">
+        <v>18.502725460899999</v>
+      </c>
+      <c r="F114" s="2">
+        <v>103.73756404</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>10</v>
@@ -6389,22 +6425,22 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>10</v>
@@ -6412,22 +6448,22 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>10</v>
@@ -6435,22 +6471,22 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>10</v>
@@ -6458,22 +6494,22 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>10</v>
@@ -6481,22 +6517,22 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>10</v>
@@ -6504,22 +6540,22 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>10</v>
@@ -6527,22 +6563,22 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>10</v>
@@ -6550,22 +6586,22 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="E122" s="2">
-        <v>40.150807945899999</v>
-      </c>
-      <c r="F122" s="2">
-        <v>127.184350323</v>
+        <v>375</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>377</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>10</v>
@@ -6573,22 +6609,22 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>10</v>
@@ -6596,22 +6632,22 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>31</v>
+        <v>383</v>
+      </c>
+      <c r="E124" s="2">
+        <v>40.150807945899999</v>
+      </c>
+      <c r="F124" s="2">
+        <v>127.184350323</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>10</v>
@@ -6619,22 +6655,22 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>31</v>
+        <v>386</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>10</v>
@@ -6642,7 +6678,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>189</v>
@@ -6651,7 +6687,7 @@
         <v>389</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>31</v>
@@ -6665,7 +6701,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>189</v>
@@ -6674,7 +6710,7 @@
         <v>389</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>31</v>
@@ -6688,7 +6724,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>189</v>
@@ -6697,7 +6733,7 @@
         <v>389</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>31</v>
@@ -6711,7 +6747,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>189</v>
@@ -6720,7 +6756,7 @@
         <v>389</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>31</v>
@@ -6734,7 +6770,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>189</v>
@@ -6743,7 +6779,7 @@
         <v>389</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>31</v>
@@ -6757,22 +6793,22 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>405</v>
+        <v>31</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>406</v>
+        <v>31</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>10</v>
@@ -6780,22 +6816,22 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>409</v>
+        <v>31</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>410</v>
+        <v>31</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>10</v>
@@ -6803,22 +6839,22 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="E133" s="2">
-        <v>35.022758144999997</v>
-      </c>
-      <c r="F133" s="2">
-        <v>38.504432305999998</v>
+        <v>404</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>406</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>10</v>
@@ -6826,22 +6862,22 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>10</v>
@@ -6849,22 +6885,22 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>420</v>
+        <v>412</v>
+      </c>
+      <c r="E135" s="2">
+        <v>35.022758144999997</v>
+      </c>
+      <c r="F135" s="2">
+        <v>38.504432305999998</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>10</v>
@@ -6872,22 +6908,22 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>10</v>
@@ -6895,22 +6931,22 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>10</v>
@@ -6918,22 +6954,22 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="E138" s="2">
-        <v>23.753006961000001</v>
-      </c>
-      <c r="F138" s="2">
-        <v>120.950311941</v>
+        <v>422</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>424</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>10</v>
@@ -6941,22 +6977,22 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>431</v>
+        <v>949</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>432</v>
+        <v>950</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>432</v>
+        <v>950</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>433</v>
+        <v>951</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>434</v>
+        <v>952</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>10</v>
@@ -6964,22 +7000,22 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="E140" s="2">
-        <v>16.6428226166</v>
-      </c>
-      <c r="F140" s="2">
-        <v>106.30113248799999</v>
+        <v>426</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>428</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>10</v>
@@ -6987,22 +7023,22 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>440</v>
+        <v>430</v>
+      </c>
+      <c r="E141" s="2">
+        <v>23.753006961000001</v>
+      </c>
+      <c r="F141" s="2">
+        <v>120.950311941</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>10</v>
@@ -7010,22 +7046,22 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>442</v>
+        <v>189</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>10</v>
@@ -7033,22 +7069,22 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>442</v>
+        <v>189</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>449</v>
+        <v>436</v>
+      </c>
+      <c r="E143" s="2">
+        <v>16.6428226166</v>
+      </c>
+      <c r="F143" s="2">
+        <v>106.30113248799999</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>10</v>
@@ -7056,22 +7092,22 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>442</v>
+        <v>189</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>10</v>
@@ -7079,22 +7115,22 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>10</v>
@@ -7102,22 +7138,22 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>10</v>
@@ -7125,22 +7161,22 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>10</v>
@@ -7148,22 +7184,22 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>10</v>
@@ -7171,22 +7207,22 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>10</v>
@@ -7194,22 +7230,22 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>10</v>
@@ -7217,22 +7253,22 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>10</v>
@@ -7240,22 +7276,22 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>10</v>
@@ -7263,22 +7299,22 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>10</v>
@@ -7286,22 +7322,22 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>10</v>
@@ -7309,22 +7345,22 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>10</v>
@@ -7332,22 +7368,22 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>10</v>
@@ -7355,22 +7391,22 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>10</v>
@@ -7378,22 +7414,22 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>10</v>
@@ -7401,22 +7437,22 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>10</v>
@@ -7424,22 +7460,22 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>10</v>
@@ -7447,22 +7483,22 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>10</v>
@@ -7470,22 +7506,22 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>10</v>
@@ -7493,22 +7529,22 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>10</v>
@@ -7516,22 +7552,22 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>10</v>
@@ -7539,22 +7575,22 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>10</v>
@@ -7562,22 +7598,22 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>10</v>
@@ -7585,22 +7621,22 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>10</v>
@@ -7608,22 +7644,22 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>10</v>
@@ -7631,22 +7667,22 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>10</v>
@@ -7654,22 +7690,22 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>10</v>
@@ -7677,22 +7713,22 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="E171" s="2">
-        <v>47.195067807900003</v>
-      </c>
-      <c r="F171" s="2">
-        <v>28.4611524643</v>
+        <v>547</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>549</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>10</v>
@@ -7700,22 +7736,22 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="E172" s="2">
-        <v>41.594894833200001</v>
-      </c>
-      <c r="F172" s="2">
-        <v>21.683956725000002</v>
+        <v>551</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>553</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>10</v>
@@ -7723,22 +7759,22 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>10</v>
@@ -7746,22 +7782,22 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>569</v>
+        <v>559</v>
+      </c>
+      <c r="E174" s="2">
+        <v>47.195067807900003</v>
+      </c>
+      <c r="F174" s="2">
+        <v>28.4611524643</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>10</v>
@@ -7769,22 +7805,22 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>573</v>
+        <v>561</v>
+      </c>
+      <c r="E175" s="2">
+        <v>41.594894833200001</v>
+      </c>
+      <c r="F175" s="2">
+        <v>21.683956725000002</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>10</v>
@@ -7792,22 +7828,22 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>10</v>
@@ -7815,22 +7851,22 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>10</v>
@@ -7838,22 +7874,22 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>10</v>
@@ -7861,22 +7897,22 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>10</v>
@@ -7884,22 +7920,22 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>10</v>
@@ -7907,22 +7943,22 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>10</v>
@@ -7930,22 +7966,22 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>10</v>
@@ -7953,22 +7989,22 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>442</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>10</v>
@@ -7976,76 +8012,76 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>607</v>
+        <v>442</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>855</v>
+        <v>596</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>856</v>
+        <v>597</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>809</v>
+        <v>10</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>607</v>
+        <v>442</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>858</v>
+        <v>600</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>859</v>
+        <v>601</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>857</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>607</v>
+        <v>442</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>855</v>
+        <v>604</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>860</v>
+        <v>605</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>809</v>
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>607</v>
@@ -8054,13 +8090,13 @@
         <v>608</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>855</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>809</v>
@@ -8068,7 +8104,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>607</v>
@@ -8077,21 +8113,21 @@
         <v>608</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>809</v>
+        <v>857</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>607</v>
@@ -8100,21 +8136,21 @@
         <v>608</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>865</v>
+        <v>855</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>864</v>
+        <v>809</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>607</v>
@@ -8123,13 +8159,13 @@
         <v>608</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>809</v>
@@ -8137,7 +8173,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>607</v>
@@ -8146,13 +8182,13 @@
         <v>608</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>809</v>
@@ -8160,7 +8196,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>607</v>
@@ -8169,105 +8205,105 @@
         <v>608</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>809</v>
+        <v>864</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>627</v>
+        <v>608</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>628</v>
+        <v>867</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>629</v>
+        <v>868</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>10</v>
+        <v>809</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>631</v>
+        <v>608</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>632</v>
+        <v>869</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>633</v>
+        <v>870</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>10</v>
+        <v>809</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>635</v>
+        <v>608</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>636</v>
+        <v>871</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>637</v>
+        <v>872</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>10</v>
+        <v>809</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>10</v>
@@ -8275,22 +8311,22 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>10</v>
@@ -8298,22 +8334,22 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>10</v>
@@ -8321,22 +8357,22 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>10</v>
@@ -8344,22 +8380,22 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>10</v>
@@ -8367,22 +8403,22 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>10</v>
@@ -8390,22 +8426,22 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>10</v>
@@ -8413,22 +8449,22 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>10</v>
@@ -8436,76 +8472,76 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>873</v>
+        <v>660</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>874</v>
+        <v>661</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>809</v>
+        <v>10</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>875</v>
+        <v>664</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>876</v>
+        <v>665</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>877</v>
+        <v>10</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>607</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>878</v>
+        <v>668</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>879</v>
+        <v>669</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>880</v>
+        <v>10</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>607</v>
@@ -8514,21 +8550,21 @@
         <v>671</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>883</v>
+        <v>809</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>607</v>
@@ -8537,21 +8573,21 @@
         <v>671</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>607</v>
@@ -8560,21 +8596,21 @@
         <v>671</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>809</v>
+        <v>880</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>607</v>
@@ -8583,21 +8619,21 @@
         <v>671</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>809</v>
+        <v>883</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>607</v>
@@ -8606,21 +8642,21 @@
         <v>671</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>607</v>
@@ -8629,21 +8665,21 @@
         <v>671</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>896</v>
+        <v>809</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>607</v>
@@ -8652,21 +8688,21 @@
         <v>671</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>899</v>
+        <v>809</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>607</v>
@@ -8675,21 +8711,21 @@
         <v>671</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>607</v>
@@ -8698,21 +8734,21 @@
         <v>671</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>607</v>
@@ -8721,21 +8757,21 @@
         <v>671</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>809</v>
+        <v>899</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>607</v>
@@ -8744,21 +8780,21 @@
         <v>671</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>607</v>
@@ -8767,21 +8803,21 @@
         <v>671</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>607</v>
@@ -8790,21 +8826,21 @@
         <v>671</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>916</v>
+        <v>809</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>607</v>
@@ -8813,21 +8849,21 @@
         <v>671</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>607</v>
@@ -8836,21 +8872,21 @@
         <v>671</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>607</v>
@@ -8859,21 +8895,21 @@
         <v>671</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>607</v>
@@ -8882,21 +8918,21 @@
         <v>671</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>607</v>
@@ -8905,21 +8941,21 @@
         <v>671</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>607</v>
@@ -8928,21 +8964,21 @@
         <v>671</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>607</v>
@@ -8951,21 +8987,21 @@
         <v>671</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>607</v>
@@ -8974,105 +9010,105 @@
         <v>671</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>720</v>
+        <v>607</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>721</v>
+        <v>671</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="E228" s="2">
-        <v>-79.406307499999997</v>
-      </c>
-      <c r="F228" s="2">
-        <v>0.31493120000000002</v>
+        <v>714</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>933</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>809</v>
+        <v>934</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>720</v>
+        <v>607</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>723</v>
+        <v>671</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>811</v>
+        <v>935</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>812</v>
+        <v>936</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>809</v>
+        <v>937</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>720</v>
+        <v>607</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>723</v>
+        <v>671</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>813</v>
+        <v>938</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>814</v>
+        <v>939</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>809</v>
+        <v>940</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>720</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>816</v>
+        <v>721</v>
+      </c>
+      <c r="E231" s="2">
+        <v>-79.406307499999997</v>
+      </c>
+      <c r="F231" s="2">
+        <v>0.31493120000000002</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>809</v>
@@ -9080,7 +9116,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>720</v>
@@ -9089,13 +9125,13 @@
         <v>723</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>809</v>
@@ -9103,7 +9139,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>720</v>
@@ -9112,13 +9148,13 @@
         <v>723</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>809</v>
@@ -9126,7 +9162,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>720</v>
@@ -9135,13 +9171,13 @@
         <v>723</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>809</v>
@@ -9149,7 +9185,7 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>720</v>
@@ -9158,13 +9194,13 @@
         <v>723</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>809</v>
@@ -9172,91 +9208,91 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>720</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>738</v>
+        <v>723</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>739</v>
+        <v>819</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>740</v>
+        <v>820</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>10</v>
+        <v>809</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>720</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>742</v>
+        <v>723</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>743</v>
+        <v>821</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>744</v>
+        <v>822</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>10</v>
+        <v>809</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>720</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>747</v>
+        <v>823</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>748</v>
+        <v>824</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>10</v>
+        <v>809</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>10</v>
@@ -9264,22 +9300,22 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>10</v>
@@ -9287,76 +9323,76 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>828</v>
+        <v>747</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>829</v>
+        <v>748</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>830</v>
+        <v>10</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>750</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>831</v>
+        <v>752</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>832</v>
+        <v>753</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>833</v>
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>750</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>837</v>
+        <v>756</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>838</v>
+        <v>757</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>834</v>
+        <v>10</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>750</v>
@@ -9365,21 +9401,21 @@
         <v>759</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>750</v>
@@ -9388,21 +9424,21 @@
         <v>759</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>750</v>
@@ -9411,21 +9447,21 @@
         <v>759</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>292</v>
+        <v>764</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>750</v>
@@ -9434,21 +9470,21 @@
         <v>759</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>825</v>
+        <v>839</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>826</v>
+        <v>840</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>750</v>
@@ -9457,21 +9493,21 @@
         <v>759</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>750</v>
@@ -9480,21 +9516,21 @@
         <v>759</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>750</v>
@@ -9503,105 +9539,105 @@
         <v>759</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>298</v>
+        <v>771</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>853</v>
+        <v>825</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>854</v>
+        <v>826</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>852</v>
+        <v>827</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>750</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>778</v>
+        <v>846</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>779</v>
+        <v>847</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>10</v>
+        <v>848</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>750</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>781</v>
+        <v>759</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>781</v>
+        <v>296</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>782</v>
+        <v>850</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>783</v>
+        <v>851</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>10</v>
+        <v>849</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>750</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>785</v>
+        <v>759</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>785</v>
+        <v>298</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>786</v>
+        <v>853</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>787</v>
+        <v>854</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>10</v>
+        <v>852</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>750</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="E254" s="2">
-        <v>4.0039882000000002</v>
-      </c>
-      <c r="F254" s="2">
-        <v>-52.999997999999998</v>
+        <v>777</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>779</v>
       </c>
       <c r="G254" s="1" t="s">
         <v>10</v>
@@ -9609,22 +9645,22 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>750</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>10</v>
@@ -9632,22 +9668,22 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>750</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>10</v>
@@ -9655,22 +9691,22 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="B257" s="1" t="s">
         <v>750</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>799</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>801</v>
+        <v>789</v>
+      </c>
+      <c r="E257" s="2">
+        <v>4.0039882000000002</v>
+      </c>
+      <c r="F257" s="2">
+        <v>-52.999997999999998</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>10</v>
@@ -9678,22 +9714,22 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>750</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>10</v>
@@ -9701,24 +9737,93 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>750</v>
       </c>
       <c r="C259" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="G259" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="G260" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="G261" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C262" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="D259" s="1" t="s">
+      <c r="D262" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="E259" s="2" t="s">
+      <c r="E262" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="F259" s="2">
+      <c r="F262" s="2">
         <v>-66.169397250800003</v>
       </c>
-      <c r="G259" s="1" t="s">
+      <c r="G262" s="1" t="s">
         <v>10</v>
       </c>
     </row>
